--- a/excel/Excel_Master_Report.xlsx
+++ b/excel/Excel_Master_Report.xlsx
@@ -899,7 +899,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Avvik = Regnskap - Budsjett. Negativt avvik = Grønt (Mindreforbruk). Positivt avvik = Rødt (Merforbruk).</t>
+          <t>Avvik = Budsjett - Regnskap. Positivt avvik = Grønt (Mindreforbruk). Negativt avvik = Rødt (Merforbruk).</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>16.10.2026 kl. 14:41</t>
+          <t>17.10.2026 kl. 12:57</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 5df3b17d2d06af8b7da01d3637ef634888bbac71ff473b7a63d530a84f47603e</t>
+          <t>SHA-256: 4db34bc04b4f12229828ac50a177c784491327b513b393b76690475c5c7d65f9</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>[Regnskap YTD] - [Budsjett YTD]</t>
+          <t>[Budsjett YTD] - [Regnskap YTD]</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Netto avvik i NOK. Positiv = Merforbruk (Rød), Negativ = Mindreforbruk (Grønn)</t>
+          <t>Netto avvik i NOK. Positiv = Mindreforbruk (Grønn), Negativ = Merforbruk (Rød)</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>SWITCH(TRUE(), [Avvik YTD %] &lt; -0.02, 'Green', [Avvik YTD %] &gt; 0.02, 'Red', 'Amber')</t>
+          <t>SWITCH(TRUE(), [Avvik YTD %] &lt; -0.02, 'Red', [Avvik YTD %] &gt; 0.02, 'Green', 'Amber')</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -3851,10 +3851,10 @@
         <v>47426244</v>
       </c>
       <c r="F6" s="70" t="n">
-        <v>-2913328</v>
+        <v>2913328</v>
       </c>
       <c r="G6" s="52" t="n">
-        <v>-0.058</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -3875,10 +3875,10 @@
         <v>36080000</v>
       </c>
       <c r="F7" s="70" t="n">
-        <v>2489000</v>
+        <v>-2489000</v>
       </c>
       <c r="G7" s="52" t="n">
-        <v>0.074</v>
+        <v>-0.074</v>
       </c>
     </row>
   </sheetData>
@@ -3978,15 +3978,15 @@
         </is>
       </c>
       <c r="C7" s="71">
-        <f>B5-B6</f>
+        <f>B6-B5</f>
         <v/>
       </c>
       <c r="D7" s="72" t="n">
-        <v>-424328</v>
+        <v>424328</v>
       </c>
       <c r="E7" s="59" t="inlineStr">
         <is>
-          <t>Beregner konsern avvik YTD</t>
+          <t>Beregner konsern avvik YTD (Budsjett - Regnskap)</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
         <v/>
       </c>
       <c r="D8" s="72" t="n">
-        <v>-0.00505</v>
+        <v>0.00505</v>
       </c>
       <c r="E8" s="59" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="C9" s="71">
-        <f>"Konsern: Regnskap er "&amp;TEXT(ABS(B7)/1000000,"0.0")&amp;" M kr "&amp;IF(B7&lt;0,"lavere enn budsjett","høyere enn budsjett")</f>
+        <f>"Konsern: Regnskap er "&amp;TEXT(ABS(B7)/1000000,"0.0")&amp;" M kr "&amp;IF(B7&gt;0,"lavere enn budsjett","høyere enn budsjett")</f>
         <v/>
       </c>
       <c r="D9" s="72" t="inlineStr">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Filterkontekst: Konsern samlet  |  Budsjettnivå: Alle virksomhetsområder  |  Periode: YTD Aug-2026  |  Fortegnsregel: Avvik = Regnskap - Budsjett</t>
+          <t xml:space="preserve">  Filterkontekst: Konsern samlet  |  Budsjettnivå: Alle virksomhetsområder  |  Periode: YTD Aug-2026  |  Fortegnsregel: Avvik = Budsjett - Regnskap</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       <c r="F6" s="19" t="n"/>
       <c r="G6" s="19" t="n"/>
       <c r="H6" s="25" t="n">
-        <v>-424328</v>
+        <v>424328</v>
       </c>
       <c r="I6" s="21" t="n"/>
       <c r="J6" s="21" t="n"/>
       <c r="K6" s="26" t="n">
-        <v>32306652</v>
+        <v>-32306652</v>
       </c>
       <c r="L6" s="23" t="n"/>
       <c r="M6" s="23" t="n"/>
@@ -4784,14 +4784,14 @@
       <c r="G7" s="19" t="n"/>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>● Gunstig (-0.5 % avvik)</t>
+          <t>● Gunstig (+0.5 % avvik)</t>
         </is>
       </c>
       <c r="I7" s="21" t="n"/>
       <c r="J7" s="21" t="n"/>
       <c r="K7" s="29" t="inlineStr">
         <is>
-          <t>● Ugunstig (+38.5 % merforbruk)</t>
+          <t>● Ugunstig (-38.5 % merforbruk)</t>
         </is>
       </c>
       <c r="L7" s="23" t="n"/>
@@ -4916,10 +4916,10 @@
         <v>10200000</v>
       </c>
       <c r="E14" s="37" t="n">
-        <v>-350000</v>
+        <v>350000</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>-0.034</v>
+        <v>0.034</v>
       </c>
       <c r="G14" s="39" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
         <v>10300000</v>
       </c>
       <c r="E15" s="43" t="n">
-        <v>-150000</v>
+        <v>150000</v>
       </c>
       <c r="F15" s="44" t="n">
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="G15" s="45" t="inlineStr">
         <is>
@@ -5012,10 +5012,10 @@
         <v>10450000</v>
       </c>
       <c r="E16" s="46" t="n">
-        <v>750000</v>
+        <v>-750000</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G16" s="42" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         <v>10500000</v>
       </c>
       <c r="E17" s="43" t="n">
-        <v>-100000</v>
+        <v>100000</v>
       </c>
       <c r="F17" s="44" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="G17" s="45" t="inlineStr">
         <is>
@@ -5108,10 +5108,10 @@
         <v>10500000</v>
       </c>
       <c r="E18" s="43" t="n">
-        <v>100000</v>
+        <v>-100000</v>
       </c>
       <c r="F18" s="44" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="G18" s="45" t="inlineStr">
         <is>
@@ -5156,10 +5156,10 @@
         <v>11000000</v>
       </c>
       <c r="E19" s="46" t="n">
-        <v>800000</v>
+        <v>-800000</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>0.073</v>
+        <v>-0.073</v>
       </c>
       <c r="G19" s="42" t="inlineStr">
         <is>
@@ -5180,10 +5180,10 @@
         <v>9500000</v>
       </c>
       <c r="E20" s="37" t="n">
-        <v>-400000</v>
+        <v>400000</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>-0.042</v>
+        <v>0.042</v>
       </c>
       <c r="G20" s="39" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
         <v>11480572</v>
       </c>
       <c r="E21" s="37" t="n">
-        <v>-1074328</v>
+        <v>1074328</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>-0.094</v>
+        <v>0.094</v>
       </c>
       <c r="G21" s="39" t="inlineStr">
         <is>
@@ -5219,8 +5219,8 @@
       <c r="B23" s="48" t="inlineStr">
         <is>
           <t>ℹ️ FORTEGNSLOGIKK &amp; METODEFORKLARING (EDWARD TUFTE STANDARD):
-• Avvik er strengt definert som: Avvik = Regnskap - Budsjett. For utgifter betyr negativt tall at kommunen har brukt MINDRE enn budsjett (gunstig / besparelse = Grønt).
-• Positivt tall betyr at utgiftene overstiger budsjettet (ugunstig / merforbruk = Rødt). Toleransebåndet er satt til ± 2,0 % (Gult).
+• Avvik er strengt definert som: Avvik = Budsjett - Regnskap. For utgifter betyr positivt tall at kommunen har brukt MINDRE enn budsjett (gunstig / mindreforbruk = Grønt).
+• Negativt tall betyr at utgiftene overstiger budsjettet (ugunstig / merforbruk = Rødt). Toleransebåndet er satt til ± 2,0 % (Gult).
 • Alle datagrunnlag stammer fra SQLite Golden Record og er kryptografisk forseglet iht. Stage-Gate Port 9 for Kommunerevisjonen.</t>
         </is>
       </c>
@@ -5345,7 +5345,7 @@
       <c r="C5" s="19" t="n"/>
       <c r="D5" s="19" t="n"/>
       <c r="E5" s="26" t="n">
-        <v>4097000</v>
+        <v>-4097000</v>
       </c>
       <c r="F5" s="23" t="n"/>
       <c r="G5" s="23" t="n"/>
@@ -5365,7 +5365,7 @@
       <c r="D6" s="19" t="n"/>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>● Merforbruk (+12.8 %)</t>
+          <t>● Merforbruk (-12.8 %)</t>
         </is>
       </c>
       <c r="F6" s="23" t="n"/>
@@ -5445,10 +5445,10 @@
         <v>31400000</v>
       </c>
       <c r="F10" s="46" t="n">
-        <v>3600000</v>
+        <v>-3600000</v>
       </c>
       <c r="G10" s="52" t="n">
-        <v>0.129</v>
+        <v>-0.129</v>
       </c>
       <c r="H10" s="50" t="inlineStr">
         <is>
@@ -5479,10 +5479,10 @@
         <v>2750000</v>
       </c>
       <c r="F11" s="46" t="n">
-        <v>250000</v>
+        <v>-250000</v>
       </c>
       <c r="G11" s="52" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="H11" s="50" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         <v>1180000</v>
       </c>
       <c r="F12" s="37" t="n">
-        <v>-20000</v>
+        <v>20000</v>
       </c>
       <c r="G12" s="52" t="n">
-        <v>-0.017</v>
+        <v>0.017</v>
       </c>
       <c r="H12" s="50" t="inlineStr">
         <is>
@@ -5547,10 +5547,10 @@
         <v>1620000</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>220000</v>
+        <v>-220000</v>
       </c>
       <c r="G13" s="52" t="n">
-        <v>0.157</v>
+        <v>-0.157</v>
       </c>
       <c r="H13" s="50" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
         <v>1130000</v>
       </c>
       <c r="F14" s="46" t="n">
-        <v>47000</v>
+        <v>-47000</v>
       </c>
       <c r="G14" s="52" t="n">
-        <v>0.043</v>
+        <v>-0.043</v>
       </c>
       <c r="H14" s="50" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
       <c r="C5" s="19" t="n"/>
       <c r="D5" s="19" t="n"/>
       <c r="E5" s="26" t="n">
-        <v>7775460</v>
+        <v>-7775460</v>
       </c>
       <c r="F5" s="23" t="n"/>
       <c r="G5" s="23" t="n"/>
@@ -5690,7 +5690,7 @@
       <c r="D6" s="19" t="n"/>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>● Merforbruk (+19.6 %)</t>
+          <t>● Merforbruk (-19.6 %)</t>
         </is>
       </c>
       <c r="F6" s="23" t="n"/>
@@ -5765,10 +5765,10 @@
         <v>27800000</v>
       </c>
       <c r="F10" s="46" t="n">
-        <v>3300000</v>
+        <v>-3300000</v>
       </c>
       <c r="G10" s="52" t="n">
-        <v>0.135</v>
+        <v>-0.135</v>
       </c>
       <c r="H10" s="50" t="inlineStr">
         <is>
@@ -5794,10 +5794,10 @@
         <v>6850000</v>
       </c>
       <c r="F11" s="46" t="n">
-        <v>2650000</v>
+        <v>-2650000</v>
       </c>
       <c r="G11" s="52" t="n">
-        <v>0.631</v>
+        <v>-0.631</v>
       </c>
       <c r="H11" s="50" t="inlineStr">
         <is>
@@ -5823,10 +5823,10 @@
         <v>3420000</v>
       </c>
       <c r="F12" s="46" t="n">
-        <v>1320000</v>
+        <v>-1320000</v>
       </c>
       <c r="G12" s="52" t="n">
-        <v>0.629</v>
+        <v>-0.629</v>
       </c>
       <c r="H12" s="50" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>382656</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>382656</v>
+        <v>-382656</v>
       </c>
       <c r="G13" s="52" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="50" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>-2980000</v>
       </c>
       <c r="F14" s="46" t="n">
-        <v>520000</v>
+        <v>-520000</v>
       </c>
       <c r="G14" s="52" t="n">
         <v>-0.149</v>
@@ -6888,10 +6888,10 @@
         <v>18197000</v>
       </c>
       <c r="H5" s="46" t="n">
-        <v>2468000</v>
+        <v>-2468000</v>
       </c>
       <c r="I5" s="52" t="n">
-        <v>0.157</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -6922,10 +6922,10 @@
         <v>847000</v>
       </c>
       <c r="H6" s="46" t="n">
-        <v>645000</v>
+        <v>-645000</v>
       </c>
       <c r="I6" s="52" t="n">
-        <v>3.193</v>
+        <v>-3.193</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -6956,10 +6956,10 @@
         <v>4216000</v>
       </c>
       <c r="H7" s="46" t="n">
-        <v>431000</v>
+        <v>-431000</v>
       </c>
       <c r="I7" s="52" t="n">
-        <v>0.114</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -6990,10 +6990,10 @@
         <v>436000</v>
       </c>
       <c r="H8" s="46" t="n">
-        <v>379000</v>
+        <v>-379000</v>
       </c>
       <c r="I8" s="52" t="n">
-        <v>6.649</v>
+        <v>-6.649</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -7024,10 +7024,10 @@
         <v>27800000</v>
       </c>
       <c r="H9" s="46" t="n">
-        <v>3300000</v>
+        <v>-3300000</v>
       </c>
       <c r="I9" s="52" t="n">
-        <v>0.135</v>
+        <v>-0.135</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -7058,10 +7058,10 @@
         <v>6850000</v>
       </c>
       <c r="H10" s="46" t="n">
-        <v>2650000</v>
+        <v>-2650000</v>
       </c>
       <c r="I10" s="52" t="n">
-        <v>0.631</v>
+        <v>-0.631</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -7092,10 +7092,10 @@
         <v>3420000</v>
       </c>
       <c r="H11" s="46" t="n">
-        <v>1320000</v>
+        <v>-1320000</v>
       </c>
       <c r="I11" s="52" t="n">
-        <v>0.629</v>
+        <v>-0.629</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -7126,10 +7126,10 @@
         <v>382656</v>
       </c>
       <c r="H12" s="46" t="n">
-        <v>382656</v>
+        <v>-382656</v>
       </c>
       <c r="I12" s="52" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
